--- a/event_registration_forms/015_process_digitization_summit_registration--event_registration_forms.xlsx
+++ b/event_registration_forms/015_process_digitization_summit_registration--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'attendee'}</t>
+          <t>attendee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Attendee'}</t>
+          <t>Attendee</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'presenter'}</t>
+          <t>presenter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Presenter'}</t>
+          <t>Presenter</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'sponsor'}</t>
+          <t>sponsor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Sponsor'}</t>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair'}</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair'}</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'service_dog'}</t>
+          <t>service_dog</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Service Dog'}</t>
+          <t>Service Dog</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'no_accessibility_needs'}</t>
+          <t>no_accessibility_needs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'No Accessibility Needs'}</t>
+          <t>No Accessibility Needs</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'track_a'}</t>
+          <t>track_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Track A'}</t>
+          <t>Track A</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'track_b'}</t>
+          <t>track_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Track B'}</t>
+          <t>Track B</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'track_c'}</t>
+          <t>track_c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Track C'}</t>
+          <t>Track C</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'onsite'}</t>
+          <t>onsite</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Onsite'}</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'confirmed_-_online'}</t>
+          <t>confirmed_-_online</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Confirmed - Online'}</t>
+          <t>Confirmed - Online</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'no_show'}</t>
+          <t>no_show</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'No Show'}</t>
+          <t>No Show</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'attendee'}</t>
+          <t>attendee</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Attendee'}</t>
+          <t>Attendee</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'presenter'}</t>
+          <t>presenter</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Presenter'}</t>
+          <t>Presenter</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'sponsor'}</t>
+          <t>sponsor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Sponsor'}</t>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'new_attendee'}</t>
+          <t>new_attendee</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'New Attendee'}</t>
+          <t>New Attendee</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'returning_attendee'}</t>
+          <t>returning_attendee</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Returning Attendee'}</t>
+          <t>Returning Attendee</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'speaker'}</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Speaker'}</t>
+          <t>Speaker</t>
         </is>
       </c>
     </row>
